--- a/static/oldsite/187/SAR_2021.xlsx
+++ b/static/oldsite/187/SAR_2021.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92487D94-565D-4803-956C-6D3DFB5E3BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -14,12 +15,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="106">
   <si>
     <t>Mauro</t>
   </si>
@@ -247,9 +251,6 @@
   </si>
   <si>
     <t>Palau</t>
-  </si>
-  <si>
-    <t>Marmillata</t>
   </si>
   <si>
     <t>ITI G. M. Angioy</t>
@@ -345,7 +346,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -782,57 +783,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -867,7 +868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -902,7 +903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
@@ -937,7 +938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -972,7 +973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1007,7 +1008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>16</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1077,7 +1078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1147,7 +1148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>26</v>
       </c>
@@ -1182,7 +1183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>28</v>
       </c>
@@ -1217,7 +1218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>30</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
@@ -1287,7 +1288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
@@ -1357,7 +1358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
@@ -1392,7 +1393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>42</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>44</v>
       </c>
@@ -1462,7 +1463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
@@ -1497,7 +1498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
@@ -1532,7 +1533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>52</v>
       </c>
@@ -1567,7 +1568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>54</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>59</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>61</v>
       </c>
@@ -1672,7 +1673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>63</v>
       </c>
@@ -1707,7 +1708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>65</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>70</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>72</v>
       </c>
@@ -1812,16 +1813,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="2">
-        <v>37990</v>
-      </c>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
       <c r="D30" s="1">
         <v>3</v>
       </c>
@@ -1832,27 +1827,27 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B31" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C31" s="2">
         <v>38196</v>
@@ -1867,27 +1862,27 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="B32" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C32" s="2">
         <v>38365</v>
@@ -1902,14 +1897,14 @@
         <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J32" s="1" t="s">
         <v>5</v>
       </c>
@@ -1917,12 +1912,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C33" s="2">
         <v>38230</v>
@@ -1937,27 +1932,27 @@
         <v>3</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="J33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="2">
         <v>38295</v>
@@ -1972,14 +1967,14 @@
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J34" s="1" t="s">
         <v>5</v>
       </c>
@@ -1987,12 +1982,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C35" s="2">
         <v>37959</v>
@@ -2007,14 +2002,14 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J35" s="1" t="s">
         <v>5</v>
       </c>
@@ -2022,12 +2017,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2">
         <v>38230</v>
@@ -2042,14 +2037,14 @@
         <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J36" s="1" t="s">
         <v>5</v>
       </c>
@@ -2057,12 +2052,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="2">
         <v>38374</v>
@@ -2077,14 +2072,14 @@
         <v>7</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J37" s="1" t="s">
         <v>5</v>
       </c>
@@ -2092,12 +2087,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C38" s="2">
         <v>38345</v>
@@ -2112,14 +2107,14 @@
         <v>8</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="J38" s="1" t="s">
         <v>5</v>
       </c>
@@ -2127,12 +2122,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="10">
         <v>38331</v>
@@ -2147,13 +2142,13 @@
         <v>9</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H39" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>5</v>
